--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,419 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121980490</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barrskog Tolvforsskogen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613727</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6731081</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121980399</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90236</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barrskog Tolvforsskogen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6731126</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121980444</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog Tolvforsskogen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>613710</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6731049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Aina Pihlgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121980398</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90236</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barrskog Tolvforsskogen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613615</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6731062</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121980399</v>
+        <v>121980444</v>
       </c>
       <c r="B4" t="n">
-        <v>90236</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613658</v>
+        <v>613710</v>
       </c>
       <c r="R4" t="n">
-        <v>6731126</v>
+        <v>6731049</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -961,6 +961,11 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -978,17 +983,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Stina Hällholm, Aina Pihlgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121980444</v>
+        <v>121980399</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>90236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613710</v>
+        <v>613658</v>
       </c>
       <c r="R5" t="n">
-        <v>6731049</v>
+        <v>6731126</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,11 +1068,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aina Pihlgren</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121980444</v>
+        <v>121980399</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>90287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613710</v>
+        <v>613658</v>
       </c>
       <c r="R3" t="n">
-        <v>6731049</v>
+        <v>6731126</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,11 +859,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aina Pihlgren</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -990,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121980398</v>
+        <v>121980444</v>
       </c>
       <c r="B5" t="n">
-        <v>90287</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613615</v>
+        <v>613710</v>
       </c>
       <c r="R5" t="n">
-        <v>6731062</v>
+        <v>6731049</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,6 +1063,11 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Stina Hällholm, Aina Pihlgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121980399</v>
+        <v>121980398</v>
       </c>
       <c r="B6" t="n">
         <v>90287</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613658</v>
+        <v>613615</v>
       </c>
       <c r="R6" t="n">
-        <v>6731126</v>
+        <v>6731062</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121980399</v>
+        <v>121980490</v>
       </c>
       <c r="B3" t="n">
-        <v>90287</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5741</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613658</v>
+        <v>613727</v>
       </c>
       <c r="R3" t="n">
-        <v>6731126</v>
+        <v>6731081</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,17 +876,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121980490</v>
+        <v>121980398</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>90297</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613727</v>
+        <v>613615</v>
       </c>
       <c r="R4" t="n">
-        <v>6731081</v>
+        <v>6731062</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121980398</v>
+        <v>121980399</v>
       </c>
       <c r="B6" t="n">
-        <v>90287</v>
+        <v>90297</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613615</v>
+        <v>613658</v>
       </c>
       <c r="R6" t="n">
-        <v>6731062</v>
+        <v>6731126</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121980490</v>
+        <v>121980444</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613727</v>
+        <v>613710</v>
       </c>
       <c r="R3" t="n">
-        <v>6731081</v>
+        <v>6731049</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,6 +859,11 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,17 +881,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Stina Hällholm, Aina Pihlgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121980398</v>
+        <v>121980490</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5741</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613615</v>
+        <v>613727</v>
       </c>
       <c r="R4" t="n">
-        <v>6731062</v>
+        <v>6731081</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,17 +983,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121980444</v>
+        <v>121980398</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>90297</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613710</v>
+        <v>613615</v>
       </c>
       <c r="R5" t="n">
-        <v>6731049</v>
+        <v>6731062</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,11 +1068,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aina Pihlgren</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 69255-2020 artfynd.xlsx
+++ b/artfynd/A 69255-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121980444</v>
+        <v>121980490</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>97151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613710</v>
+        <v>613727</v>
       </c>
       <c r="R3" t="n">
-        <v>6731049</v>
+        <v>6731081</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,11 +859,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,17 +876,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aina Pihlgren</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121980490</v>
+        <v>121980444</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613727</v>
+        <v>613710</v>
       </c>
       <c r="R4" t="n">
-        <v>6731081</v>
+        <v>6731049</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,6 +961,11 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +983,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Stina Hällholm, Aina Pihlgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -993,7 +993,7 @@
         <v>121980398</v>
       </c>
       <c r="B5" t="n">
-        <v>90297</v>
+        <v>90309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>121980399</v>
       </c>
       <c r="B6" t="n">
-        <v>90297</v>
+        <v>90309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
